--- a/Apartment Hunt — Columbus (Oct 2026).xlsx
+++ b/Apartment Hunt — Columbus (Oct 2026).xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kirkham\Documents\Vault\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kirkham/Library/CloudStorage/ProtonDrive-jason@kirkham.cloud-folder/Vault/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B70F1F9-52EA-46C9-8850-01A468A34E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7E0F89-304B-BF46-94DF-E8872C8C206B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Apartments" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Apartments!$A$1:$W$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Apartments!$A$1:$W$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="128">
   <si>
     <t>Ruled out</t>
   </si>
@@ -107,6 +107,9 @@
     <t>Net effective $/mo</t>
   </si>
   <si>
+    <t>x</t>
+  </si>
+  <si>
     <t>Normandy Columbus — 315 E Long St, 43215</t>
   </si>
   <si>
@@ -125,6 +128,9 @@
     <t>35 min (1.6 mi)</t>
   </si>
   <si>
+    <t>Toured 7/20 — ruled out. Disliked pool location; poor fitness center.</t>
+  </si>
+  <si>
     <t>X</t>
   </si>
   <si>
@@ -242,6 +248,9 @@
     <t>73 min (3.4 mi)</t>
   </si>
   <si>
+    <t>Ruled out — Thrive-managed (poor management reviews).</t>
+  </si>
+  <si>
     <t>8 on the Park at GVX — 1366 Olivine Dr, 43215</t>
   </si>
   <si>
@@ -383,7 +392,34 @@
     <t>9 min (0.4 mi, est.)</t>
   </si>
   <si>
-    <t>Would need to go with larger unit.  No concessions.</t>
+    <t>Lusso — 370 Carmelina Ave, 43201</t>
+  </si>
+  <si>
+    <t>livinglusso.com</t>
+  </si>
+  <si>
+    <t>6 min (0.3 mi, est.)</t>
+  </si>
+  <si>
+    <t>Gravity — 480 W Broad St, 43215</t>
+  </si>
+  <si>
+    <t>gravitycolumbus.com</t>
+  </si>
+  <si>
+    <t>8 min (3.5 mi)</t>
+  </si>
+  <si>
+    <t>62 min (3.2 mi, est.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toured 7/21 - really like it.  Top choice currently.  </t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Toured; has potential but limited availibility</t>
   </si>
 </sst>
 </file>
@@ -472,7 +508,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -526,9 +562,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -536,6 +569,49 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -767,15 +843,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:W22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="41.140625" customWidth="1"/>
-    <col min="3" max="3" width="34.28515625" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="2" max="2" width="41.1640625" customWidth="1"/>
+    <col min="3" max="4" width="22" customWidth="1"/>
     <col min="5" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="51.28515625" style="15" customWidth="1"/>
+    <col min="8" max="8" width="51.33203125" style="15" customWidth="1"/>
     <col min="9" max="10" width="8" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
@@ -790,7 +865,7 @@
     <col min="22" max="22" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" ht="32" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -861,26 +936,31 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="2"/>
+        <v>29</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -891,34 +971,34 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="5"/>
       <c r="W2" s="12" t="str">
-        <f t="shared" ref="W2:W20" si="0">IF(AND(I2&lt;&gt;"",R2&lt;&gt;""),I2*(R2-S2)/R2+T2+U2,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" spans="1:23" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+        <f>IF(AND(I2&lt;&gt;"",R2&lt;&gt;""),I2*(R2-S2)/R2+T2+U2,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="28" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -930,28 +1010,31 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="5"/>
       <c r="W3" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+        <f>IF(AND(I3&lt;&gt;"",R3&lt;&gt;""),I3*(R3-S3)/R3+T3+U3,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="B4" s="16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>37</v>
+        <v>25</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="E4" s="16"/>
       <c r="F4" s="16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" s="23"/>
+        <v>41</v>
+      </c>
+      <c r="H4" s="22"/>
       <c r="I4" s="16"/>
       <c r="J4" s="16"/>
       <c r="K4" s="16"/>
@@ -962,30 +1045,33 @@
       <c r="P4" s="16"/>
       <c r="Q4" s="16"/>
       <c r="W4" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+        <f>IF(AND(I4&lt;&gt;"",R4&lt;&gt;""),I4*(R4-S4)/R4+T4+U4,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="24" t="s">
+        <v>23</v>
+      </c>
       <c r="B5" s="16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" s="23"/>
+        <v>46</v>
+      </c>
+      <c r="H5" s="22"/>
       <c r="I5" s="16"/>
       <c r="J5" s="16"/>
       <c r="K5" s="16"/>
@@ -996,142 +1082,144 @@
       <c r="P5" s="16"/>
       <c r="Q5" s="16"/>
       <c r="W5" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="11" t="s">
+        <f>IF(AND(I5&lt;&gt;"",R5&lt;&gt;""),I5*(R5-S5)/R5+T5+U5,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="9"/>
+      <c r="D6" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" s="22"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
       <c r="W6" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:23" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="I7" s="7">
-        <v>1609</v>
-      </c>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="N7" s="6"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="9"/>
-      <c r="R7">
-        <v>13</v>
-      </c>
-      <c r="S7">
-        <v>1</v>
-      </c>
-      <c r="W7" s="12">
-        <f t="shared" si="0"/>
-        <v>1485.2307692307693</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="H8" s="23"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
+        <f>IF(AND(I6&lt;&gt;"",R6&lt;&gt;""),I6*(R6-S6)/R6+T6+U6,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="5"/>
+      <c r="W7" s="12" t="str">
+        <f>IF(AND(I7&lt;&gt;"",R7&lt;&gt;""),I7*(R7-S7)/R7+T7+U7,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="5"/>
       <c r="W8" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:23" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+        <f>IF(AND(I8&lt;&gt;"",R8&lt;&gt;""),I8*(R8-S8)/R8+T8+U8,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
       <c r="B9" s="2" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="5" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="H9" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -1142,28 +1230,33 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="5"/>
       <c r="W9" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:23" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+        <f>IF(AND(I9&lt;&gt;"",R9&lt;&gt;""),I9*(R9-S9)/R9+T9+U9,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
       <c r="B10" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H10" s="2"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -1174,60 +1267,74 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="5"/>
       <c r="W10" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:23" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="5" t="s">
+        <f>IF(AND(I10&lt;&gt;"",R10&lt;&gt;""),I10*(R10-S10)/R10+T10+U10,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="9"/>
+      <c r="W11" s="12" t="str">
+        <f>IF(AND(I11&lt;&gt;"",R11&lt;&gt;""),I11*(R11-S11)/R11+T11+U11,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="5"/>
-      <c r="W11" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:23" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="H12" s="2"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -1238,139 +1345,144 @@
       <c r="P12" s="3"/>
       <c r="Q12" s="5"/>
       <c r="W12" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:23" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="9"/>
+        <f>IF(AND(I12&lt;&gt;"",R12&lt;&gt;""),I12*(R12-S12)/R12+T12+U12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="26"/>
+      <c r="B13" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="H13" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
       <c r="W13" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:23" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G14" s="5" t="s">
+        <f>IF(AND(I13&lt;&gt;"",R13&lt;&gt;""),I13*(R13-S13)/R13+T13+U13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="9"/>
+      <c r="W14" s="12" t="str">
+        <f>IF(AND(I14&lt;&gt;"",R14&lt;&gt;""),I14*(R14-S14)/R14+T14+U14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15" s="8"/>
+      <c r="F15" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="9"/>
+      <c r="W15" s="12" t="str">
+        <f>IF(AND(I15&lt;&gt;"",R15&lt;&gt;""),I15*(R15-S15)/R15+T15+U15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="5"/>
-      <c r="W14" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:23" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="5"/>
-      <c r="W15" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:23" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="F16" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="G16" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="H16" s="17"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="H16" s="17" t="s">
+        <v>70</v>
+      </c>
       <c r="I16" s="18"/>
       <c r="J16" s="18"/>
       <c r="K16" s="18"/>
@@ -1379,125 +1491,215 @@
       <c r="N16" s="17"/>
       <c r="O16" s="18"/>
       <c r="P16" s="18"/>
-      <c r="Q16" s="22"/>
+      <c r="Q16" s="21"/>
       <c r="W16" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="2:23" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="C17" s="18" t="s">
+        <f>IF(AND(I16&lt;&gt;"",R16&lt;&gt;""),I16*(R16-S16)/R16+T16+U16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="G17" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" s="32"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="32"/>
+      <c r="O17" s="34"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="37"/>
+      <c r="W17" s="12" t="str">
+        <f>IF(AND(I17&lt;&gt;"",R17&lt;&gt;""),I17*(R17-S17)/R17+T17+U17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="H18" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="I18" s="34">
+        <v>1609</v>
+      </c>
+      <c r="J18" s="34"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="34"/>
+      <c r="M18" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="N18" s="32"/>
+      <c r="O18" s="34"/>
+      <c r="P18" s="34"/>
+      <c r="Q18" s="37"/>
+      <c r="R18">
+        <v>13</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="W18" s="12">
+        <f>IF(AND(I18&lt;&gt;"",R18&lt;&gt;""),I18*(R18-S18)/R18+T18+U18,"")</f>
+        <v>1485.2307692307693</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" ht="13" x14ac:dyDescent="0.15">
+      <c r="B19" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="G19" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="H19" s="38"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="33"/>
+      <c r="N19" s="33"/>
+      <c r="O19" s="33"/>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="33"/>
+      <c r="W19" s="12" t="str">
+        <f>IF(AND(I19&lt;&gt;"",R19&lt;&gt;""),I19*(R19-S19)/R19+T19+U19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="14" x14ac:dyDescent="0.15">
+      <c r="A20" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="E17" s="19"/>
-      <c r="F17" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="H17" s="17"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="18"/>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="22"/>
-      <c r="W17" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="2:23" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" s="18" t="s">
+      <c r="G20" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="H20" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="31"/>
+      <c r="W20" s="12" t="str">
+        <f>IF(AND(I20&lt;&gt;"",R20&lt;&gt;""),I20*(R20-S20)/R20+T20+U20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:23" ht="13" x14ac:dyDescent="0.15">
+      <c r="B21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="E18" s="19"/>
-      <c r="F18" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="G18" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="H18" s="17"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="18"/>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="22"/>
-      <c r="W18" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="2:23" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C19" t="s">
-        <v>108</v>
-      </c>
-      <c r="D19" t="s">
-        <v>109</v>
-      </c>
-      <c r="F19" t="s">
-        <v>99</v>
-      </c>
-      <c r="G19" t="s">
-        <v>110</v>
-      </c>
-      <c r="W19" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="2:23" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B20" t="s">
+      <c r="G21" t="s">
+        <v>120</v>
+      </c>
+      <c r="W21" s="12" t="str">
+        <f>IF(AND(I21&lt;&gt;"",R21&lt;&gt;""),I21*(R21-S21)/R21+T21+U21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:23" ht="14" x14ac:dyDescent="0.15">
+      <c r="B22" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" t="s">
         <v>111</v>
       </c>
-      <c r="C20" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" t="s">
-        <v>112</v>
-      </c>
-      <c r="F20" t="s">
-        <v>113</v>
-      </c>
-      <c r="G20" t="s">
-        <v>114</v>
-      </c>
-      <c r="W20" s="12" t="str">
-        <f t="shared" si="0"/>
+      <c r="D22" t="s">
+        <v>115</v>
+      </c>
+      <c r="F22" t="s">
+        <v>116</v>
+      </c>
+      <c r="G22" t="s">
+        <v>117</v>
+      </c>
+      <c r="H22" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="W22" s="12" t="str">
+        <f>IF(AND(I22&lt;&gt;"",R22&lt;&gt;""),I22*(R22-S22)/R22+T22+U22,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W20" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W18">
-      <sortCondition ref="C1:C18"/>
+  <autoFilter ref="A1:W22" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W22">
+      <sortCondition ref="A1:A22"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="A2:W20">
+  <conditionalFormatting sqref="A2:W22">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$A2&lt;&gt;""</formula>
     </cfRule>
@@ -1505,18 +1707,18 @@
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="C6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="C7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="C9" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="C10" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="C11" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="C12" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="C13" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="C14" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="C15" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="C16" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="C17" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="C18" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="C17" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C18" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="C7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="C8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="C9" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="C10" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="C11" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="C12" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="C20" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="C14" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="C15" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="C16" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
